--- a/compiler_practice_functions.xlsx
+++ b/compiler_practice_functions.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="412">
   <si>
     <t xml:space="preserve">Ассемблерные инструкции компиляторов по функциям</t>
   </si>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">.LBB2_1: </t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB2_1:        cmpl    $5, i</t>
+    <t xml:space="preserve">.LBB2_1:    </t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .L19</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">    cmpl    $5, i(%rip)</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB2_4        movl    -4(%rbp), %eax</t>
+    <t xml:space="preserve">    cmpl    $5, i</t>
   </si>
   <si>
     <t xml:space="preserve">.L20:</t>
@@ -214,93 +214,99 @@
     <t xml:space="preserve">    jge    .LBB2_4</t>
   </si>
   <si>
+    <t xml:space="preserve">    jge    .LBB2_4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    j5(%rip), %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    j5(%rip), %eax</t>
+  </si>
+  <si>
     <t xml:space="preserve">    addl    j5, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    j5(%rip), %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %eax, k5        movl    i, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    j5(%rip), %eax</t>
+    <t xml:space="preserve">    addl    %edx, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %eax, k5(%rip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %eax, k5        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    i(%rip), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    i, %eax</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    $1, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %edx, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %eax, k5(%rip)</t>
+    <t xml:space="preserve">    movl    %eax, i(%rip)</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, i</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    i(%rip), %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">    jmp    .LBB2_1</t>
   </si>
   <si>
+    <t xml:space="preserve">.L19:</t>
+  </si>
+  <si>
     <t xml:space="preserve">.LBB2_4:</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %eax, i(%rip)</t>
+    <t xml:space="preserve">    movl    k5(%rip), %esi</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    k5, %esi</t>
   </si>
   <si>
+    <t xml:space="preserve">    cmpl    $4, %eax</t>
+  </si>
+  <si>
     <t xml:space="preserve">    movabsq    $.L.str, %rdi</t>
   </si>
   <si>
-    <t xml:space="preserve">.L19:</t>
+    <t xml:space="preserve">    jle    .L20</t>
   </si>
   <si>
     <t xml:space="preserve">    movb    $0, %al</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    k5(%rip), %esi</t>
+    <t xml:space="preserve">    movl    k5(%rip), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    callq    printf@PLT</t>
   </si>
   <si>
     <t xml:space="preserve">    callq    printf</t>
   </si>
   <si>
-    <t xml:space="preserve">    cmpl    $4, %eax</t>
+    <t xml:space="preserve">    leaq    .LC0(%rip), %rdx</t>
   </si>
   <si>
     <t xml:space="preserve">    addq    $16, %rsp</t>
   </si>
   <si>
-    <t xml:space="preserve">    jle    .L20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    k5(%rip), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    callq    printf@PLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    leaq    .LC0(%rip), %rdx</t>
-  </si>
-  <si>
     <t xml:space="preserve">    movl    %eax, %esi</t>
   </si>
   <si>
+    <t xml:space="preserve">    movq    %rdx, %rdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    $0, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    call    printf@PLT</t>
+  </si>
+  <si>
     <t xml:space="preserve">.Lfunc_end2:</t>
   </si>
   <si>
-    <t xml:space="preserve">    movq    %rdx, %rdi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    $0, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    call    printf@PLT</t>
-  </si>
-  <si>
     <t xml:space="preserve">    leave</t>
   </si>
   <si>
@@ -361,10 +367,7 @@
     <t xml:space="preserve">    .p2align 3</t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB3_1:        cmpl    $5, i(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB3_1:        cmpl    $5, i</t>
+    <t xml:space="preserve">.LBB3_1:    </t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .L22</t>
@@ -373,69 +376,57 @@
     <t xml:space="preserve">.L5:</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB3_4        movl    -4(%rbp), %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">.L23:</t>
   </si>
   <si>
     <t xml:space="preserve">    imull    j5(%rip), %esi</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    j5(%rip), %ecx</t>
+    <t xml:space="preserve">    jge    .LBB3_4     </t>
   </si>
   <si>
     <t xml:space="preserve">    leaq    .L.str(%rip), %r14</t>
   </si>
   <si>
+    <t xml:space="preserve">   movl    -4(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    j5(%rip), %r14d</t>
+  </si>
+  <si>
     <t xml:space="preserve">    movl    j5, %ecx</t>
   </si>
   <si>
-    <t xml:space="preserve">    imull    i(%rip), %ecx</t>
+    <t xml:space="preserve">    .p2align    4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %edi, k5(%rip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    imull    %eax, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %ebx, %esi</t>
   </si>
   <si>
     <t xml:space="preserve">    imull    i, %ecx</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    j5(%rip), %r14d</t>
-  </si>
-  <si>
     <t xml:space="preserve">    addl    %ecx, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    .p2align    4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %edi, k5(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    %eax, %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %ebx, %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB3_1:        imull    j5(%rip), %esi</t>
+    <t xml:space="preserve">    movl    %ebx, %esi</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, k5</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %ebx, %esi</t>
+    <t xml:space="preserve">    leal    1(%rax), %esi</t>
   </si>
   <si>
     <t xml:space="preserve">    movq    %r14, %rdi</t>
   </si>
   <si>
-    <t xml:space="preserve">    leal    1(%rax), %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    callq    printf@PLT        movl    i(%rip), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    callq    printf        movl    i, %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">    leal    (%rbx,%r14), %esi</t>
   </si>
   <si>
@@ -445,150 +436,150 @@
     <t xml:space="preserve">    cmpl    $4, %esi</t>
   </si>
   <si>
+    <t xml:space="preserve">    callq    printf    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    callq    printf     </t>
+  </si>
+  <si>
     <t xml:space="preserve">    jle    .L5</t>
   </si>
   <si>
+    <t xml:space="preserve">   movl    i, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leal    (%rbx,%r14,2), %esi</t>
+  </si>
+  <si>
     <t xml:space="preserve">    jmp    .LBB3_1</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB3_4:</t>
   </si>
   <si>
-    <t xml:space="preserve">    leal    (%rbx,%r14,2), %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB3_5:        cmpl    $5, i(%rip)</t>
-  </si>
-  <si>
     <t xml:space="preserve">    jl    .LBB3_1</t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB3_5:        cmpl    $5, i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB3_8        movl    -4(%rbp), %eax</t>
+    <t xml:space="preserve">.L6:</t>
   </si>
   <si>
     <t xml:space="preserve">        movl    $0, i(%rip)</t>
   </si>
   <si>
-    <t xml:space="preserve">.L6:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    k5(%rip), %eax</t>
+    <t xml:space="preserve">.L22:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB3_5:    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leal    (%r14,%r14,2), %esi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %esi, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB3_8    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jle    .L23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    imull    %ebx, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB3_3:    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    imull    %edx, %eax</t>
   </si>
   <si>
     <t xml:space="preserve">    imull    k5, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">.L22:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    i(%rip), %eax</t>
+    <t xml:space="preserve">    jmp    .L24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %eax, i5(%rip)</t>
   </si>
   <si>
     <t xml:space="preserve">    imull    i, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %eax, i5(%rip)</t>
+    <t xml:space="preserve">    imull    %ebx, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L25:</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, i5</t>
   </si>
   <si>
-    <t xml:space="preserve">    leal    (%r14,%r14,2), %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %esi, %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB3_3:        movl    k5(%rip), %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jle    .L23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    %ebx, %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    %ebx, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    %edx, %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">    imull    %esi, %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    jmp    .L24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L25:</t>
-  </si>
-  <si>
     <t xml:space="preserve">    leal    (%rbx,%r14,4), %ebp</t>
   </si>
   <si>
     <t xml:space="preserve">    imull    -4(%rbp), %eax</t>
   </si>
   <si>
+    <t xml:space="preserve">    movl    %ebp, k5(%rip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %eax, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %ebp, %esi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    i(%rip), %ecx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jle    .L6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leal    1(%rcx), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    popq    %rbx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    $0, i5(%rip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_def_cfa_offset 8</t>
+  </si>
+  <si>
     <t xml:space="preserve">    jmp    .LBB3_5</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %ebp, k5(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %eax, %edx</t>
+    <t xml:space="preserve">    cmpl    $4, %ecx</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB3_8:</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    i(%rip), %ecx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    leal    1(%rcx), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %ebp, %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jle    .L6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    $4, %ecx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    popq    %rbx</t>
-  </si>
-  <si>
     <t xml:space="preserve">    jl    .LBB3_3</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    $0, i5(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .cfi_def_cfa_offset 8</t>
+    <t xml:space="preserve">        addq    $8, %rsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LFE14:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    $1, i(%rip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    imull    %ebp, %ebx</t>
   </si>
   <si>
     <t xml:space="preserve">.Lfunc_end3:</t>
   </si>
   <si>
-    <t xml:space="preserve">        addq    $8, %rsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LFE14:</t>
-  </si>
-  <si>
     <t xml:space="preserve">    popq    %r14</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    $1, i(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    imull    %ebp, %ebx</t>
-  </si>
-  <si>
     <t xml:space="preserve">    movl    %ebx, i5(%rip)</t>
   </si>
   <si>
@@ -631,10 +622,7 @@
     <t xml:space="preserve">    leaq    ivector4(%rip), %rbx</t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB4_1:        cmpl    $6, i(%rip)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB4_1:        cmpl    $6, i</t>
+    <t xml:space="preserve">.LBB4_1:    </t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .L27</t>
@@ -643,13 +631,13 @@
     <t xml:space="preserve">.L11:</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB4_4        movslq    i(%rip), %rcx</t>
+    <t xml:space="preserve">    cmpl    $6, i(%rip)</t>
   </si>
   <si>
     <t xml:space="preserve">    leaq    ivector4(%rip), %r14</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB4_4        movslq    i, %rax</t>
+    <t xml:space="preserve">    cmpl    $6, i</t>
   </si>
   <si>
     <t xml:space="preserve">.L28:</t>
@@ -658,87 +646,96 @@
     <t xml:space="preserve">    cltq</t>
   </si>
   <si>
+    <t xml:space="preserve">    jge    .LBB4_4    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leaq    .L.str(%rip), %rbx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    xorl    %edx, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movslq    i(%rip), %rcx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movslq    i, %rax</t>
+  </si>
+  <si>
     <t xml:space="preserve">    leaq    ivector4(%rip), %rax</t>
   </si>
   <si>
-    <t xml:space="preserve">    leaq    .L.str(%rip), %rbx</t>
-  </si>
-  <si>
     <t xml:space="preserve">    movw    $0, ivector4(,%rax,2)</t>
   </si>
   <si>
-    <t xml:space="preserve">    xorl    %edx, %edx</t>
+    <t xml:space="preserve">    leaq    (%rax,%rax), %rdx</t>
   </si>
   <si>
     <t xml:space="preserve">    movw    $0, (%rax,%rcx,2)</t>
   </si>
   <si>
-    <t xml:space="preserve">    movslq    i, %rax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movslq    i(%rip), %rcx</t>
+    <t xml:space="preserve">.LBB4_1:   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movw    %dx, (%rbx,%rax,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     cltq</t>
   </si>
   <si>
     <t xml:space="preserve">    movswl    ivector4(,%rax,2), %esi</t>
   </si>
   <si>
-    <t xml:space="preserve">    leaq    (%rax,%rax), %rdx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB4_1:        cltq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movw    %dx, (%rbx,%rax,2)</t>
+    <t xml:space="preserve">    movw    $0, (%rdx,%rax)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movw    $0, (%r14,%rax,2)</t>
   </si>
   <si>
     <t xml:space="preserve">    movswl    (%rax,%rcx,2), %esi</t>
   </si>
   <si>
-    <t xml:space="preserve">    movw    $0, (%r14,%rax,2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movw    $0, (%rdx,%rax)</t>
-  </si>
-  <si>
     <t xml:space="preserve">    movq    %rbx, %rdi</t>
   </si>
   <si>
     <t xml:space="preserve">    movq    $0, ivector4(%rip)</t>
   </si>
   <si>
+    <t xml:space="preserve">    callq    printf@PLT    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movzwl    (%rdx,%rax), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    $5, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cwtl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jle    .L11</t>
+  </si>
+  <si>
     <t xml:space="preserve">    jmp    .LBB4_1</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB4_4:</t>
   </si>
   <si>
-    <t xml:space="preserve">    movzwl    (%rdx,%rax), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    $5, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cwtl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jle    .L11</t>
-  </si>
-  <si>
     <t xml:space="preserve">    cmpl    $5, %ecx</t>
   </si>
   <si>
+    <t xml:space="preserve">    movw    $0, ivector4+8(%rip)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    jl    .LBB4_1</t>
   </si>
   <si>
-    <t xml:space="preserve">    movw    $0, ivector4+8(%rip)</t>
+    <t xml:space="preserve">.LFE15:</t>
   </si>
   <si>
     <t xml:space="preserve">.Lfunc_end4:</t>
   </si>
   <si>
-    <t xml:space="preserve">.LFE15:</t>
-  </si>
-  <si>
     <t xml:space="preserve">    movw    $0, ivector4+10(%rip)</t>
   </si>
   <si>
@@ -820,7 +817,7 @@
     <t xml:space="preserve">    .cfi_offset 12, -32</t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB5_1:        movl    -4(%rbp), %eax</t>
+    <t xml:space="preserve">.LBB5_1:    </t>
   </si>
   <si>
     <t xml:space="preserve">    .cfi_def_cfa_offset 56</t>
@@ -835,387 +832,408 @@
     <t xml:space="preserve">    movl    %edi, %r12d</t>
   </si>
   <si>
+    <t xml:space="preserve">    .cfi_offset %r14, -32</t>
+  </si>
+  <si>
     <t xml:space="preserve">    cmpl    -8(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    .cfi_offset %r14, -32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_13        movl    -8(%rbp), %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">    .cfi_def_cfa_offset 64</t>
   </si>
   <si>
     <t xml:space="preserve">    .cfi_offset %r15, -24</t>
   </si>
   <si>
+    <t xml:space="preserve">    jge    .LBB5_13     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_offset %rbx, -56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .L31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_offset 6, -40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   movl    -8(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_offset %r12, -48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %r8d, %ebp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    -8(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %edx, %ebp</t>
+  </si>
+  <si>
     <t xml:space="preserve">    cmpl    -12(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    .cfi_offset %rbx, -56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .L31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .cfi_offset 6, -40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_10        movl    -12(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .cfi_offset %r12, -48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %r8d, %ebp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    -8(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %edx, %ebp</t>
+    <t xml:space="preserve">    .cfi_offset %r13, -40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %ecx, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_10    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %edx, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .L32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    -12(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %esi, %r14d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_offset 3, -48</t>
   </si>
   <si>
     <t xml:space="preserve">    cmpl    -16(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    .cfi_offset %r13, -40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %ecx, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_8        movl    -16(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %edx, %r15d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .L32</t>
+    <t xml:space="preserve">    movl    %esi, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_8     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %esi, %edi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .L33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %edi, %esi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   movl    -16(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %ecx, %r12d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jl    .LBB5_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    -16(%rbp), %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jg    .L15</t>
   </si>
   <si>
     <t xml:space="preserve">    cmpl    -20(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %esi, %r14d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    -12(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .cfi_offset 3, -48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_6        movl    -20(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %esi, %ebx</t>
+    <t xml:space="preserve">    movl    %edx, %r14d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_8:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jmp    .L16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_6    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r14d, %r12d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .L38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .p2align 4,,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %edi, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_9:</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -16(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    cmpl    %esi, %edi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .L33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    %edi, %esi</t>
+    <t xml:space="preserve">    addl    %r15d, %r14d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %eax, -16(%rbp)</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, -16(%rbp)</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %ecx, %r12d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jl    .LBB5_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    -16(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jg    .L15</t>
+    <t xml:space="preserve">    jge    .LBB5_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r12d, %r14d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jmp    .L35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %r13d, %ebp</t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .LBB5_7</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %edx, %r14d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_8:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jmp    .L16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_6:        jmp    .LBB5_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %r14d, %r12d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .L38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .p2align 4,,10</t>
+    <t xml:space="preserve">        leaq    .L.str(%rip), %r13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %ebp, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L33:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .L18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_6:    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jmp    .LBB5_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r14d, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %r14d, %r13d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jmp    .LBB5_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %ebx, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %eax, -12(%rbp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jl    .L23</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB5_7:</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %edi, %r15d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_9:</t>
+    <t xml:space="preserve">.LBB5_7:    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %r12d, %ebx</t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .LBB5_9</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %r15d, %r14d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %eax, -16(%rbp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %r12d, %r14d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jmp    .L35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    %r13d, %ebp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        leaq    .L.str(%rip), %r13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %ebp, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L33:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .L18</t>
+    <t xml:space="preserve">.L32:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jle    .L16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movq    %r13, %rdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    popq    %r12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L15:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %eax, -8(%rbp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cmpl    %ebx, %ebp</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -12(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    jmp    .LBB5_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %r14d, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    %r14d, %r13d</t>
+    <t xml:space="preserve">    jg    .L24</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, -12(%rbp)</t>
   </si>
   <si>
-    <t xml:space="preserve">    movl    %ebx, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %eax, -12(%rbp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jl    .L23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_7:        addl    %r14d, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    %r12d, %ebx</t>
+    <t xml:space="preserve">.LBB5_8:     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    popq    %r15</t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .LBB5_12</t>
   </si>
   <si>
-    <t xml:space="preserve">    movq    %r13, %rdi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L32:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jle    .L16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_10:        movl    -12(%rbp), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    popq    %r12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L15:</t>
+    <t xml:space="preserve">   cmpl    %ebx, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_10:    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_2:     </t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -8(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %eax, -8(%rbp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cmpl    %ebx, %ebp</t>
+    <t xml:space="preserve">   cmpl    %r14d, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jmp    .L30</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    %eax, -8(%rbp)</t>
   </si>
   <si>
-    <t xml:space="preserve">    jg    .L24</t>
+    <t xml:space="preserve">    jge    .LBB5_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L38:</t>
   </si>
   <si>
     <t xml:space="preserve">    movl    -8(%rbp), %esi</t>
   </si>
   <si>
-    <t xml:space="preserve">.LBB5_8:        cmpl    %ebx, %r15d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    popq    %r15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_2:        cmpl    %r14d, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_7</t>
+    <t xml:space="preserve">        cmpl    %r12d, %r14d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_6:     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   .cfi_def_cfa_offset 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L36:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cmpl    %ebp, %r12d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L16:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.L31:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %ebx, %r12d</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB5_11:        jmp    .LBB5_1</t>
   </si>
   <si>
-    <t xml:space="preserve">        cmpl    %r12d, %r14d</t>
+    <t xml:space="preserve">        addl    %ebp, %r12d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    %r14d, %esi</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB5_12:</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB5_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jmp    .L30</t>
+    <t xml:space="preserve">    jmp    .LBB5_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %eax, -4(%rbp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    leal    (%r12,%rbx), %eax</t>
   </si>
   <si>
     <t xml:space="preserve">    jmp    .LBB5_14</t>
   </si>
   <si>
-    <t xml:space="preserve">        cmpl    %ebp, %r12d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L38:</t>
+    <t xml:space="preserve">.L35:</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB5_13:</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB5_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_6:        .cfi_def_cfa_offset 48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        addl    %ebp, %r12d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L36:</t>
+    <t xml:space="preserve">    addl    %ebx, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_7:     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    movl    -4(%rbp), %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    .cfi_remember_state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_10:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   cmpl    %r14d, %r12d</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -4(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    jmp    .LBB5_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L16:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    %r14d, %esi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L31:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %ebx, %r12d</t>
+    <t xml:space="preserve">    addl    %eax, %edx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %ebp, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_1:        cmpl    %r15d, %r14d</t>
   </si>
   <si>
     <t xml:space="preserve">.LBB5_14:</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %ebx, %r15d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_10:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %eax, -4(%rbp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    leal    (%r12,%rbx), %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_7:        cmpl    %r14d, %r12d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.L35:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    movl    -4(%rbp), %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    .cfi_remember_state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_1:        cmpl    %r15d, %r14d</t>
+    <t xml:space="preserve">    jge    .LBB5_6        cmpl    %ebx, %r15d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r15d, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_5        cmpl    %ebp, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    jge    .LBB5_7        addl    %ebp, %ebx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addq    $8, %rsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    addl    %r13d, %eax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.LBB5_5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    popq    %r13</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    -20(%rbp), %eax</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %r15d, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_6        cmpl    %ebx, %r15d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %eax, %edx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %ebp, %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">    addq    $32, %rsp</t>
   </si>
   <si>
-    <t xml:space="preserve">    jge    .LBB5_5        cmpl    %ebp, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addq    $8, %rsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jge    .LBB5_7        addl    %ebp, %ebx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.LBB5_5:</t>
+    <t xml:space="preserve">    addl    %r14d, %eax</t>
   </si>
   <si>
     <t xml:space="preserve">.Lfunc_end5:</t>
   </si>
   <si>
-    <t xml:space="preserve">    addl    %r13d, %eax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    popq    %r13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    addl    %r14d, %eax</t>
-  </si>
-  <si>
     <t xml:space="preserve">.LFE5:</t>
   </si>
   <si>
@@ -1228,10 +1246,10 @@
     <t xml:space="preserve">    addl    %r13d, %ebp</t>
   </si>
   <si>
+    <t xml:space="preserve">    jmp    .L20</t>
+  </si>
+  <si>
     <t xml:space="preserve">.LBB5_6:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    jmp    .L20</t>
   </si>
   <si>
     <t xml:space="preserve">    addl    %r14d, %r13d</t>
@@ -1248,7 +1266,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1278,6 +1296,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1444,7 +1468,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1606,6 +1630,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2530,7 +2558,7 @@
       <c r="D35" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="41" t="s">
         <v>61</v>
       </c>
       <c r="G35" s="40"/>
@@ -2562,8 +2590,8 @@
       <c r="D37" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="37" t="s">
-        <v>66</v>
+      <c r="F37" s="41" t="s">
+        <v>28</v>
       </c>
       <c r="G37" s="40"/>
     </row>
@@ -2576,10 +2604,10 @@
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="37" t="s">
         <v>67</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>68</v>
       </c>
       <c r="G38" s="40"/>
     </row>
@@ -2588,14 +2616,14 @@
         <v>15</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="37" t="s">
         <v>70</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>71</v>
       </c>
       <c r="G39" s="40"/>
     </row>
@@ -2604,14 +2632,14 @@
         <v>16</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="41" t="s">
         <v>72</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>73</v>
       </c>
       <c r="G40" s="40"/>
       <c r="I40" s="1"/>
@@ -2627,14 +2655,14 @@
         <v>17</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="37" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G41" s="40"/>
     </row>
@@ -2643,14 +2671,14 @@
         <v>18</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F42" s="37" t="s">
         <v>75</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>76</v>
       </c>
       <c r="G42" s="40"/>
     </row>
@@ -2659,14 +2687,14 @@
         <v>19</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G43" s="40"/>
     </row>
@@ -2675,14 +2703,14 @@
         <v>20</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C44" s="17"/>
       <c r="D44" s="37" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G44" s="40"/>
     </row>
@@ -2691,14 +2719,14 @@
         <v>21</v>
       </c>
       <c r="B45" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F45" s="37" t="s">
         <v>80</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>81</v>
       </c>
       <c r="G45" s="40"/>
     </row>
@@ -2707,14 +2735,14 @@
         <v>22</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="37" t="s">
         <v>47</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G46" s="40"/>
     </row>
@@ -2723,14 +2751,14 @@
         <v>23</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="37" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="G47" s="40"/>
     </row>
@@ -2746,7 +2774,7 @@
         <v>86</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="G48" s="40"/>
     </row>
@@ -2755,14 +2783,14 @@
         <v>25</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="37" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G49" s="40"/>
     </row>
@@ -2771,14 +2799,14 @@
         <v>26</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="37" t="s">
         <v>32</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="G50" s="40"/>
     </row>
@@ -2787,13 +2815,15 @@
         <v>27</v>
       </c>
       <c r="B51" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="F51" s="37"/>
+      <c r="F51" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="G51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2801,33 +2831,37 @@
         <v>28</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="37"/>
+      <c r="F52" s="37" t="s">
+        <v>13</v>
+      </c>
       <c r="G52" s="40"/>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="35" t="n">
         <v>29</v>
       </c>
-      <c r="B53" s="41" t="s">
-        <v>92</v>
+      <c r="B53" s="42" t="s">
+        <v>93</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="F53" s="37"/>
+        <v>94</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>94</v>
+      </c>
       <c r="G53" s="15"/>
     </row>
     <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B54" s="41" t="s">
+      <c r="B54" s="42" t="s">
         <v>33</v>
       </c>
       <c r="F54" s="37"/>
@@ -2837,8 +2871,8 @@
       <c r="A55" s="35" t="n">
         <v>31</v>
       </c>
-      <c r="B55" s="41" t="s">
-        <v>93</v>
+      <c r="B55" s="42" t="s">
+        <v>95</v>
       </c>
       <c r="F55" s="37"/>
       <c r="G55" s="15"/>
@@ -2847,7 +2881,7 @@
       <c r="A56" s="35" t="n">
         <v>32</v>
       </c>
-      <c r="B56" s="41" t="s">
+      <c r="B56" s="42" t="s">
         <v>35</v>
       </c>
       <c r="F56" s="37"/>
@@ -2857,7 +2891,7 @@
       <c r="A57" s="35" t="n">
         <v>33</v>
       </c>
-      <c r="B57" s="41" t="s">
+      <c r="B57" s="42" t="s">
         <v>14</v>
       </c>
       <c r="G57" s="15"/>
@@ -2866,17 +2900,17 @@
       <c r="A58" s="35" t="n">
         <v>34</v>
       </c>
-      <c r="B58" s="41" t="s">
+      <c r="B58" s="42" t="s">
         <v>17</v>
       </c>
       <c r="G58" s="15"/>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="42" t="n">
+      <c r="A59" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="B59" s="43" t="s">
-        <v>94</v>
+      <c r="B59" s="44" t="s">
+        <v>96</v>
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
@@ -2901,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>7</v>
@@ -2920,7 +2954,7 @@
     </row>
     <row r="62" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2942,25 +2976,25 @@
       <c r="D63" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E63" s="44" t="s">
+      <c r="E63" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="F63" s="44" t="s">
+      <c r="F63" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="45" t="s">
+      <c r="G63" s="46" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="46" t="n">
+      <c r="A64" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D64" s="33" t="s">
         <v>41</v>
@@ -2976,7 +3010,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="47" t="n">
+      <c r="A65" s="48" t="n">
         <v>2</v>
       </c>
       <c r="B65" s="14" t="s">
@@ -2989,7 +3023,7 @@
         <v>12</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F65" s="37" t="s">
         <v>12</v>
@@ -2999,14 +3033,14 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="n">
+      <c r="A66" s="48" t="n">
         <v>3</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>15</v>
@@ -3022,7 +3056,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="47" t="n">
+      <c r="A67" s="48" t="n">
         <v>4</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -3035,86 +3069,86 @@
         <v>18</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F67" s="37" t="s">
         <v>18</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="n">
+      <c r="A68" s="48" t="n">
         <v>5</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D68" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F68" s="37" t="s">
         <v>21</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="47" t="n">
+      <c r="A69" s="48" t="n">
         <v>6</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D69" s="37" t="s">
         <v>22</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F69" s="37" t="s">
         <v>22</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="47" t="n">
+      <c r="A70" s="48" t="n">
         <v>7</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D70" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F70" s="37" t="s">
         <v>49</v>
       </c>
       <c r="G70" s="38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="47" t="n">
+      <c r="A71" s="48" t="n">
         <v>8</v>
       </c>
       <c r="B71" s="14" t="s">
@@ -3127,86 +3161,86 @@
         <v>24</v>
       </c>
       <c r="E71" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F71" s="37" t="s">
         <v>24</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="47" t="n">
+      <c r="A72" s="48" t="n">
         <v>9</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E72" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F72" s="37" t="s">
         <v>55</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="47" t="n">
+      <c r="A73" s="48" t="n">
         <v>10</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G73" s="38" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="47" t="n">
+      <c r="A74" s="48" t="n">
         <v>11</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D74" s="37" t="s">
         <v>117</v>
+      </c>
+      <c r="D74" s="41" t="s">
+        <v>61</v>
       </c>
       <c r="E74" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="F74" s="37" t="s">
-        <v>117</v>
+      <c r="F74" s="41" t="s">
+        <v>61</v>
       </c>
       <c r="G74" s="38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="n">
+      <c r="A75" s="48" t="n">
         <v>12</v>
       </c>
       <c r="B75" s="14" t="s">
@@ -3222,14 +3256,14 @@
         <v>121</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G75" s="38" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="n">
+      <c r="A76" s="48" t="n">
         <v>13</v>
       </c>
       <c r="B76" s="14" t="s">
@@ -3238,67 +3272,67 @@
       <c r="C76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="37" t="s">
+      <c r="D76" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="F76" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="E76" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="G76" s="38" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="77" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="47" t="n">
+      <c r="A77" s="48" t="n">
         <v>14</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D77" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F77" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G77" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="E77" s="37" t="s">
+    </row>
+    <row r="78" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B78" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F77" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="G77" s="38" t="s">
+      <c r="C78" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="47" t="n">
-        <v>15</v>
-      </c>
-      <c r="B78" s="14" t="s">
+      <c r="D78" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>70</v>
-      </c>
       <c r="E78" s="37" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G78" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="47" t="n">
+      <c r="A79" s="48" t="n">
         <v>16</v>
       </c>
       <c r="B79" s="14" t="s">
@@ -3308,633 +3342,637 @@
         <v>43</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E79" s="37" t="s">
         <v>130</v>
       </c>
+      <c r="E79" s="41" t="s">
+        <v>119</v>
+      </c>
       <c r="F79" s="37" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="47" t="n">
+      <c r="A80" s="48" t="n">
         <v>17</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="F80" s="37" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="G80" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="47" t="n">
+      <c r="A81" s="48" t="n">
         <v>18</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="47" t="n">
+      <c r="A82" s="48" t="n">
         <v>19</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D82" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G82" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="D82" s="37" t="s">
+    </row>
+    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E82" s="37" t="s">
+      <c r="D83" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G82" s="38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="47" t="n">
-        <v>20</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D83" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>86</v>
-      </c>
       <c r="F83" s="37" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="G83" s="38" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="47" t="n">
+      <c r="A84" s="48" t="n">
         <v>21</v>
       </c>
       <c r="B84" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="E84" s="37" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="F84" s="37" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="G84" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="47" t="n">
+      <c r="A85" s="48" t="n">
         <v>22</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F85" s="41" t="s">
         <v>141</v>
-      </c>
-      <c r="D85" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="G85" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="47" t="n">
+      <c r="A86" s="48" t="n">
         <v>23</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="G86" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="47" t="n">
+      <c r="A87" s="48" t="n">
         <v>24</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E87" s="37" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G87" s="38" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="47" t="n">
+      <c r="A88" s="48" t="n">
         <v>25</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E88" s="37" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G88" s="38" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="47" t="n">
+      <c r="A89" s="48" t="n">
         <v>26</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D89" s="37" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G89" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="47" t="n">
+      <c r="A90" s="48" t="n">
         <v>27</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="E90" s="37" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="F90" s="37" t="s">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="G90" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="47" t="n">
+      <c r="A91" s="48" t="n">
         <v>28</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91" s="37" t="s">
-        <v>154</v>
+        <v>79</v>
+      </c>
+      <c r="D91" s="41" t="s">
+        <v>149</v>
       </c>
       <c r="E91" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>155</v>
+        <v>121</v>
+      </c>
+      <c r="F91" s="41" t="s">
+        <v>149</v>
       </c>
       <c r="G91" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="47" t="n">
+      <c r="A92" s="48" t="n">
         <v>29</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="E92" s="37" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="47" t="n">
+      <c r="A93" s="48" t="n">
         <v>30</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D93" s="37" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E93" s="37" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F93" s="37" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="G93" s="38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="47" t="n">
+      <c r="A94" s="48" t="n">
         <v>31</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94" s="37" t="s">
-        <v>47</v>
+        <v>154</v>
+      </c>
+      <c r="D94" s="41" t="s">
+        <v>28</v>
       </c>
       <c r="E94" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="F94" s="37" t="s">
-        <v>77</v>
+        <v>155</v>
+      </c>
+      <c r="F94" s="41" t="s">
+        <v>28</v>
       </c>
       <c r="G94" s="38" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="47" t="n">
+      <c r="A95" s="48" t="n">
         <v>32</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D95" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E95" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="E95" s="37" t="s">
-        <v>165</v>
-      </c>
       <c r="F95" s="37" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="G95" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="47" t="n">
+      <c r="A96" s="48" t="n">
         <v>33</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D96" s="37" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E96" s="37" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="G96" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="47" t="n">
+      <c r="A97" s="48" t="n">
         <v>34</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="E97" s="37" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="G97" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="47" t="n">
+      <c r="A98" s="48" t="n">
         <v>35</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E98" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="G98" s="38" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="48" t="n">
+        <v>36</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="F99" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G99" s="38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="48" t="n">
+        <v>37</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E100" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="G98" s="38" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D99" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E99" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F99" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="G99" s="38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="47" t="n">
-        <v>37</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D100" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>174</v>
-      </c>
       <c r="F100" s="37" t="s">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="G100" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="47" t="n">
+      <c r="A101" s="48" t="n">
         <v>38</v>
       </c>
       <c r="B101" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D101" s="37" t="s">
-        <v>83</v>
+        <v>74</v>
+      </c>
+      <c r="D101" s="41" t="s">
+        <v>139</v>
       </c>
       <c r="E101" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="F101" s="37" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="F101" s="41" t="s">
+        <v>139</v>
       </c>
       <c r="G101" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="47" t="n">
+      <c r="A102" s="48" t="n">
         <v>39</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="E102" s="37" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="G102" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="47" t="n">
+      <c r="A103" s="48" t="n">
         <v>40</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D103" s="37" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="E103" s="37" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="G103" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="47" t="n">
+      <c r="A104" s="48" t="n">
         <v>41</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E104" s="37" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="F104" s="37" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="G104" s="38" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="47" t="n">
+      <c r="A105" s="48" t="n">
         <v>42</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E105" s="37" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F105" s="37" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G105" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="47" t="n">
+      <c r="A106" s="48" t="n">
         <v>43</v>
       </c>
       <c r="B106" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="37"/>
+      <c r="D106" s="37" t="s">
+        <v>178</v>
+      </c>
       <c r="E106" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F106" s="37"/>
+        <v>179</v>
+      </c>
+      <c r="F106" s="37" t="s">
+        <v>178</v>
+      </c>
       <c r="G106" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
@@ -3945,197 +3983,221 @@
       <c r="O106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="47" t="n">
+      <c r="A107" s="48" t="n">
         <v>44</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D107" s="37"/>
+      <c r="D107" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="E107" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="F107" s="37"/>
+        <v>180</v>
+      </c>
+      <c r="F107" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="G107" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="47" t="n">
+      <c r="A108" s="48" t="n">
         <v>45</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D108" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F108" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G108" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B109" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D109" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E109" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F109" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G109" s="38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B110" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D110" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B111" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D111" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E111" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="D108" s="37"/>
-      <c r="E108" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" s="37"/>
-      <c r="G108" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D109" s="37"/>
-      <c r="E109" s="37" t="s">
+      <c r="F111" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="G111" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="F109" s="37"/>
-      <c r="G109" s="38" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="47" t="n">
-        <v>47</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D110" s="37"/>
-      <c r="E110" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="F110" s="37"/>
-      <c r="G110" s="38" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="47" t="n">
-        <v>48</v>
-      </c>
-      <c r="B111" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D111" s="37"/>
-      <c r="E111" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="37"/>
-      <c r="G111" s="38" t="s">
-        <v>189</v>
-      </c>
     </row>
     <row r="112" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="47" t="n">
+      <c r="A112" s="48" t="n">
         <v>49</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E112" s="37" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G112" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="47" t="n">
+      <c r="A113" s="48" t="n">
         <v>50</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="E113" s="37"/>
+        <v>187</v>
+      </c>
+      <c r="E113" s="37" t="s">
+        <v>13</v>
+      </c>
       <c r="G113" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="47" t="n">
+      <c r="A114" s="48" t="n">
         <v>51</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E114" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="E114" s="37" t="s">
+        <v>184</v>
+      </c>
       <c r="G114" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="47" t="n">
+      <c r="A115" s="48" t="n">
         <v>52</v>
       </c>
       <c r="B115" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G115" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="47" t="n">
+      <c r="A116" s="48" t="n">
         <v>53</v>
       </c>
       <c r="B116" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G116" s="38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="47" t="n">
+      <c r="A117" s="48" t="n">
         <v>54</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G117" s="38" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="47" t="n">
+      <c r="A118" s="48" t="n">
         <v>55</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="38" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="47" t="n">
+      <c r="A119" s="48" t="n">
         <v>56</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G119" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="47" t="n">
+      <c r="A120" s="48" t="n">
         <v>57</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>35</v>
       </c>
       <c r="G120" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="47" t="n">
+      <c r="A121" s="48" t="n">
         <v>58</v>
       </c>
       <c r="B121" s="14" t="s">
@@ -4146,212 +4208,212 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="47" t="n">
+      <c r="A122" s="48" t="n">
         <v>59</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>17</v>
       </c>
       <c r="G122" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="47" t="n">
+      <c r="A123" s="48" t="n">
         <v>60</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G123" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="47" t="n">
+      <c r="A124" s="48" t="n">
         <v>61</v>
       </c>
       <c r="B124" s="14"/>
       <c r="G124" s="38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="47" t="n">
+      <c r="A125" s="48" t="n">
         <v>62</v>
       </c>
       <c r="B125" s="14"/>
       <c r="G125" s="38" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="47" t="n">
+      <c r="A126" s="48" t="n">
         <v>63</v>
       </c>
-      <c r="B126" s="48"/>
+      <c r="B126" s="49"/>
       <c r="G126" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="47" t="n">
+      <c r="A127" s="48" t="n">
         <v>64</v>
       </c>
-      <c r="B127" s="48"/>
+      <c r="B127" s="49"/>
       <c r="G127" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="47" t="n">
+      <c r="A128" s="48" t="n">
         <v>65</v>
       </c>
-      <c r="B128" s="48"/>
+      <c r="B128" s="49"/>
       <c r="G128" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="47" t="n">
+      <c r="A129" s="48" t="n">
         <v>66</v>
       </c>
-      <c r="B129" s="48"/>
+      <c r="B129" s="49"/>
       <c r="G129" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="47" t="n">
+      <c r="A130" s="48" t="n">
         <v>67</v>
       </c>
-      <c r="B130" s="48"/>
+      <c r="B130" s="49"/>
       <c r="G130" s="38" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="47" t="n">
+      <c r="A131" s="48" t="n">
         <v>68</v>
       </c>
-      <c r="B131" s="48"/>
+      <c r="B131" s="49"/>
       <c r="G131" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="47" t="n">
+      <c r="A132" s="48" t="n">
         <v>69</v>
       </c>
-      <c r="B132" s="48"/>
+      <c r="B132" s="49"/>
       <c r="G132" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="47" t="n">
+      <c r="A133" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="B133" s="48"/>
+      <c r="B133" s="49"/>
       <c r="G133" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="47" t="n">
+      <c r="A134" s="48" t="n">
         <v>71</v>
       </c>
-      <c r="B134" s="48"/>
+      <c r="B134" s="49"/>
       <c r="G134" s="38" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="47" t="n">
+      <c r="A135" s="48" t="n">
         <v>72</v>
       </c>
-      <c r="B135" s="48"/>
+      <c r="B135" s="49"/>
       <c r="G135" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="47" t="n">
+      <c r="A136" s="48" t="n">
         <v>73</v>
       </c>
-      <c r="B136" s="48"/>
+      <c r="B136" s="49"/>
       <c r="G136" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="47" t="n">
+      <c r="A137" s="48" t="n">
         <v>74</v>
       </c>
-      <c r="B137" s="48"/>
+      <c r="B137" s="49"/>
       <c r="G137" s="38" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="47" t="n">
+      <c r="A138" s="48" t="n">
         <v>75</v>
       </c>
-      <c r="B138" s="48"/>
+      <c r="B138" s="49"/>
       <c r="G138" s="38" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="47" t="n">
+      <c r="A139" s="48" t="n">
         <v>76</v>
       </c>
-      <c r="B139" s="48"/>
+      <c r="B139" s="49"/>
       <c r="G139" s="38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="47" t="n">
+      <c r="A140" s="48" t="n">
         <v>77</v>
       </c>
-      <c r="B140" s="48"/>
+      <c r="B140" s="49"/>
       <c r="G140" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="47" t="n">
+      <c r="A141" s="48" t="n">
         <v>78</v>
       </c>
-      <c r="B141" s="48"/>
+      <c r="B141" s="49"/>
       <c r="G141" s="38" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="47" t="n">
+      <c r="A142" s="48" t="n">
         <v>79</v>
       </c>
-      <c r="B142" s="48"/>
+      <c r="B142" s="49"/>
       <c r="G142" s="38" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="47" t="n">
+      <c r="A143" s="48" t="n">
         <v>80</v>
       </c>
-      <c r="B143" s="48"/>
+      <c r="B143" s="49"/>
       <c r="G143" s="38" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="47" t="n">
+      <c r="A144" s="48" t="n">
         <v>81</v>
       </c>
-      <c r="B144" s="48"/>
+      <c r="B144" s="49"/>
       <c r="G144" s="38" t="s">
         <v>13</v>
       </c>
@@ -4364,16 +4426,16 @@
       <c r="O144" s="2"/>
     </row>
     <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="49" t="n">
+      <c r="A145" s="50" t="n">
         <v>82</v>
       </c>
-      <c r="B145" s="50"/>
+      <c r="B145" s="51"/>
       <c r="C145" s="20"/>
       <c r="D145" s="20"/>
       <c r="E145" s="20"/>
       <c r="F145" s="20"/>
-      <c r="G145" s="51" t="s">
-        <v>183</v>
+      <c r="G145" s="52" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4387,13 +4449,13 @@
         <v>45</v>
       </c>
       <c r="D146" s="24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E146" s="24" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F146" s="24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G146" s="25" t="n">
         <v>82</v>
@@ -4412,7 +4474,7 @@
     </row>
     <row r="148" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4445,14 +4507,14 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="46" t="n">
+      <c r="A150" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D150" s="33" t="s">
         <v>41</v>
@@ -4468,7 +4530,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="47" t="n">
+      <c r="A151" s="48" t="n">
         <v>2</v>
       </c>
       <c r="B151" s="14" t="s">
@@ -4481,24 +4543,24 @@
         <v>12</v>
       </c>
       <c r="E151" s="37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F151" s="37" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="47" t="n">
+      <c r="A152" s="48" t="n">
         <v>3</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C152" s="37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D152" s="37" t="s">
         <v>15</v>
@@ -4514,7 +4576,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="47" t="n">
+      <c r="A153" s="48" t="n">
         <v>4</v>
       </c>
       <c r="B153" s="14" t="s">
@@ -4527,7 +4589,7 @@
         <v>18</v>
       </c>
       <c r="E153" s="37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F153" s="37" t="s">
         <v>18</v>
@@ -4537,30 +4599,30 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="47" t="n">
+      <c r="A154" s="48" t="n">
         <v>5</v>
       </c>
       <c r="B154" s="14" t="s">
         <v>19</v>
       </c>
       <c r="C154" s="37" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D154" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E154" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F154" s="37" t="s">
         <v>21</v>
       </c>
       <c r="G154" s="38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="47" t="n">
+      <c r="A155" s="48" t="n">
         <v>6</v>
       </c>
       <c r="B155" s="14" t="s">
@@ -4573,7 +4635,7 @@
         <v>22</v>
       </c>
       <c r="E155" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F155" s="37" t="s">
         <v>22</v>
@@ -4583,30 +4645,30 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="47" t="n">
+      <c r="A156" s="48" t="n">
         <v>7</v>
       </c>
       <c r="B156" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C156" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D156" s="37" t="s">
         <v>49</v>
       </c>
       <c r="E156" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F156" s="37" t="s">
         <v>49</v>
       </c>
       <c r="G156" s="38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="47" t="n">
+      <c r="A157" s="48" t="n">
         <v>8</v>
       </c>
       <c r="B157" s="14" t="s">
@@ -4619,30 +4681,30 @@
         <v>24</v>
       </c>
       <c r="E157" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F157" s="37" t="s">
         <v>24</v>
       </c>
       <c r="G157" s="38" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="47" t="n">
+      <c r="A158" s="48" t="n">
         <v>9</v>
       </c>
       <c r="B158" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C158" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D158" s="37" t="s">
         <v>54</v>
       </c>
       <c r="E158" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F158" s="37" t="s">
         <v>55</v>
@@ -4652,647 +4714,661 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="47" t="n">
+      <c r="A159" s="48" t="n">
         <v>10</v>
       </c>
       <c r="B159" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C159" s="37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D159" s="37" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E159" s="37" t="s">
         <v>54</v>
       </c>
       <c r="F159" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="G159" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B160" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C160" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="D160" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E160" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="G159" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="47" t="n">
-        <v>11</v>
-      </c>
-      <c r="B160" s="14" t="s">
+      <c r="F160" s="41" t="s">
         <v>205</v>
-      </c>
-      <c r="C160" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="D160" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="E160" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="F160" s="37" t="s">
-        <v>209</v>
       </c>
       <c r="G160" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="47" t="n">
+      <c r="A161" s="48" t="n">
         <v>12</v>
       </c>
       <c r="B161" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C161" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="D161" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="E161" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="F161" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="G161" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B162" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C162" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="C161" s="37" t="s">
+      <c r="D162" s="37" t="s">
         <v>211</v>
-      </c>
-      <c r="D161" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E161" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="F161" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="G161" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="47" t="n">
-        <v>13</v>
-      </c>
-      <c r="B162" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C162" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="D162" s="37" t="s">
-        <v>216</v>
       </c>
       <c r="E162" s="37" t="s">
         <v>44</v>
       </c>
       <c r="F162" s="37" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G162" s="38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="47" t="n">
+      <c r="A163" s="48" t="n">
         <v>14</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C163" s="37" t="s">
         <v>46</v>
       </c>
       <c r="D163" s="37" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E163" s="37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F163" s="37" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G163" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="47" t="n">
+      <c r="A164" s="48" t="n">
         <v>15</v>
       </c>
       <c r="B164" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C164" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D164" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E164" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="F164" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B165" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C165" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="D165" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E165" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F165" s="37" t="s">
         <v>220</v>
-      </c>
-      <c r="C164" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D164" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E164" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="F164" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G164" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="47" t="n">
-        <v>16</v>
-      </c>
-      <c r="B165" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="C165" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="D165" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="E165" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="F165" s="37" t="s">
-        <v>79</v>
       </c>
       <c r="G165" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="47" t="n">
+      <c r="A166" s="48" t="n">
         <v>17</v>
       </c>
       <c r="B166" s="14" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C166" s="37" t="s">
         <v>44</v>
       </c>
       <c r="D166" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="E166" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="F166" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B167" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C167" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D167" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="E167" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="F167" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G167" s="38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="48" t="n">
+        <v>19</v>
+      </c>
+      <c r="B168" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C168" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D168" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E166" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="F166" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G166" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="47" t="n">
-        <v>18</v>
-      </c>
-      <c r="B167" s="14" t="s">
+      <c r="E168" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="F168" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G168" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B169" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C169" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D169" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E169" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F169" s="41" t="s">
         <v>72</v>
-      </c>
-      <c r="C167" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D167" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E167" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F167" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="G167" s="38" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="47" t="n">
-        <v>19</v>
-      </c>
-      <c r="B168" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C168" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D168" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="E168" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="F168" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="G168" s="38" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="47" t="n">
-        <v>20</v>
-      </c>
-      <c r="B169" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C169" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="D169" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E169" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F169" s="37" t="s">
-        <v>228</v>
       </c>
       <c r="G169" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="47" t="n">
+      <c r="A170" s="48" t="n">
         <v>21</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C170" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D170" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E170" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F170" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="G170" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B171" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C171" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="D171" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="E171" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="F171" s="37" t="s">
         <v>75</v>
-      </c>
-      <c r="D170" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E170" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F170" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="G170" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="47" t="n">
-        <v>22</v>
-      </c>
-      <c r="B171" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="C171" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="D171" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="E171" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="F171" s="37" t="s">
-        <v>83</v>
       </c>
       <c r="G171" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="47" t="n">
+      <c r="A172" s="48" t="n">
         <v>23</v>
       </c>
       <c r="B172" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C172" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="D172" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E172" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F172" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G172" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B173" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C173" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D173" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E173" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F173" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="C172" s="37" t="s">
+      <c r="G173" s="38" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="48" t="n">
+        <v>25</v>
+      </c>
+      <c r="B174" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C174" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="D174" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E174" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="D172" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="E172" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F172" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G172" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="47" t="n">
-        <v>24</v>
-      </c>
-      <c r="B173" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C173" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="D173" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E173" s="37" t="s">
+      <c r="F174" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="G174" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="F173" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="G173" s="38" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="47" t="n">
-        <v>25</v>
-      </c>
-      <c r="B174" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C174" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="D174" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E174" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="F174" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G174" s="38" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="175" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="47" t="n">
+      <c r="A175" s="48" t="n">
         <v>26</v>
       </c>
       <c r="B175" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C175" s="37" t="s">
         <v>14</v>
       </c>
       <c r="D175" s="37" t="s">
-        <v>34</v>
+        <v>232</v>
       </c>
       <c r="E175" s="37" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="F175" s="37" t="s">
-        <v>237</v>
+        <v>32</v>
       </c>
       <c r="G175" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="47" t="n">
+      <c r="A176" s="48" t="n">
         <v>27</v>
       </c>
       <c r="B176" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C176" s="37" t="s">
         <v>17</v>
       </c>
       <c r="D176" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="E176" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F176" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G176" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B177" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C177" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="D177" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E177" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F177" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="E176" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F176" s="37"/>
-      <c r="G176" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="B177" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C177" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="D177" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="E177" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="F177" s="37"/>
       <c r="G177" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="47" t="n">
+      <c r="A178" s="48" t="n">
         <v>29</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C178" s="52"/>
-      <c r="D178" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="C178" s="53"/>
+      <c r="D178" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="E178" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F178" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="G178" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="B179" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C179" s="53"/>
+      <c r="D179" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E179" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F178" s="37"/>
-      <c r="G178" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="B179" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C179" s="52"/>
-      <c r="D179" s="37"/>
-      <c r="E179" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="F179" s="52"/>
+      <c r="F179" s="53"/>
       <c r="G179" s="38" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="47" t="n">
+      <c r="A180" s="48" t="n">
         <v>31</v>
       </c>
       <c r="B180" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C180" s="52"/>
-      <c r="D180" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="C180" s="53"/>
+      <c r="D180" s="37" t="s">
+        <v>237</v>
+      </c>
       <c r="E180" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="F180" s="52"/>
+        <v>185</v>
+      </c>
+      <c r="F180" s="53"/>
       <c r="G180" s="38" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="B181" s="14" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="181" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="47" t="n">
-        <v>32</v>
-      </c>
-      <c r="B181" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="C181" s="52"/>
-      <c r="D181" s="52"/>
+      <c r="C181" s="53"/>
+      <c r="D181" s="53"/>
       <c r="E181" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" s="52"/>
+        <v>175</v>
+      </c>
+      <c r="F181" s="53"/>
       <c r="G181" s="38" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="47" t="n">
+      <c r="A182" s="48" t="n">
         <v>33</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C182" s="52"/>
-      <c r="D182" s="52"/>
+        <v>71</v>
+      </c>
+      <c r="C182" s="53"/>
+      <c r="D182" s="53"/>
       <c r="E182" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="53"/>
+      <c r="G182" s="38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="48" t="n">
+        <v>34</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C183" s="53"/>
+      <c r="D183" s="53"/>
+      <c r="E183" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="F182" s="52"/>
-      <c r="G182" s="38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="183" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="47" t="n">
-        <v>34</v>
-      </c>
-      <c r="B183" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="C183" s="52"/>
-      <c r="D183" s="52"/>
-      <c r="E183" s="37"/>
-      <c r="F183" s="52"/>
+      <c r="F183" s="53"/>
       <c r="G183" s="38" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="47" t="n">
+      <c r="A184" s="48" t="n">
         <v>35</v>
       </c>
       <c r="B184" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C184" s="53"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="53"/>
+      <c r="F184" s="53"/>
+      <c r="G184" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="48" t="n">
+        <v>36</v>
+      </c>
+      <c r="B185" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C185" s="53"/>
+      <c r="D185" s="53"/>
+      <c r="E185" s="53"/>
+      <c r="F185" s="53"/>
+      <c r="G185" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="C184" s="52"/>
-      <c r="D184" s="52"/>
-      <c r="E184" s="52"/>
-      <c r="F184" s="52"/>
-      <c r="G184" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="185" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="B185" s="48" t="s">
+    </row>
+    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="48" t="n">
+        <v>37</v>
+      </c>
+      <c r="B186" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C185" s="52"/>
-      <c r="D185" s="52"/>
-      <c r="E185" s="52"/>
-      <c r="F185" s="52"/>
-      <c r="G185" s="38" t="s">
+      <c r="C186" s="53"/>
+      <c r="D186" s="53"/>
+      <c r="E186" s="53"/>
+      <c r="F186" s="53"/>
+      <c r="G186" s="38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="47" t="n">
-        <v>37</v>
-      </c>
-      <c r="B186" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C186" s="52"/>
-      <c r="D186" s="52"/>
-      <c r="E186" s="52"/>
-      <c r="F186" s="52"/>
-      <c r="G186" s="38" t="s">
-        <v>243</v>
-      </c>
-    </row>
     <row r="187" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="47" t="n">
+      <c r="A187" s="48" t="n">
         <v>38</v>
       </c>
-      <c r="B187" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C187" s="52"/>
-      <c r="D187" s="52"/>
-      <c r="E187" s="52"/>
-      <c r="F187" s="52"/>
+      <c r="B187" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C187" s="53"/>
+      <c r="D187" s="53"/>
+      <c r="E187" s="53"/>
+      <c r="F187" s="53"/>
       <c r="G187" s="38" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="47" t="n">
+      <c r="A188" s="48" t="n">
         <v>39</v>
       </c>
-      <c r="B188" s="48" t="s">
+      <c r="B188" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C188" s="52"/>
-      <c r="D188" s="52"/>
-      <c r="E188" s="52"/>
-      <c r="F188" s="52"/>
+      <c r="C188" s="53"/>
+      <c r="D188" s="53"/>
+      <c r="E188" s="53"/>
+      <c r="F188" s="53"/>
       <c r="G188" s="38" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="47" t="n">
+      <c r="A189" s="48" t="n">
         <v>40</v>
       </c>
-      <c r="B189" s="48" t="s">
+      <c r="B189" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C189" s="52"/>
-      <c r="D189" s="52"/>
-      <c r="E189" s="52"/>
-      <c r="F189" s="52"/>
+      <c r="C189" s="53"/>
+      <c r="D189" s="53"/>
+      <c r="E189" s="53"/>
+      <c r="F189" s="53"/>
       <c r="G189" s="38" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="47" t="n">
+      <c r="A190" s="48" t="n">
         <v>41</v>
       </c>
-      <c r="B190" s="48" t="s">
+      <c r="B190" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C190" s="52"/>
-      <c r="D190" s="52"/>
-      <c r="E190" s="52"/>
-      <c r="F190" s="52"/>
+      <c r="C190" s="53"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="53"/>
+      <c r="F190" s="53"/>
       <c r="G190" s="15"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="49" t="n">
+      <c r="A191" s="50" t="n">
         <v>42</v>
       </c>
-      <c r="B191" s="50" t="s">
-        <v>244</v>
+      <c r="B191" s="51" t="s">
+        <v>243</v>
       </c>
       <c r="C191" s="20"/>
       <c r="D191" s="20"/>
@@ -5311,13 +5387,13 @@
         <v>28</v>
       </c>
       <c r="D192" s="24" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E192" s="24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F192" s="24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G192" s="25" t="n">
         <v>40</v>
@@ -5336,7 +5412,7 @@
     </row>
     <row r="194" customFormat="false" ht="29.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5369,30 +5445,30 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="46" t="n">
+      <c r="A196" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B196" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C196" s="33" t="s">
         <v>246</v>
       </c>
-      <c r="C196" s="33" t="s">
+      <c r="D196" s="33" t="s">
         <v>247</v>
-      </c>
-      <c r="D196" s="33" t="s">
-        <v>248</v>
       </c>
       <c r="E196" s="33" t="s">
         <v>11</v>
       </c>
       <c r="F196" s="33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G196" s="34" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="47" t="n">
+      <c r="A197" s="48" t="n">
         <v>2</v>
       </c>
       <c r="B197" s="14" t="s">
@@ -5405,7 +5481,7 @@
         <v>12</v>
       </c>
       <c r="E197" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F197" s="37" t="s">
         <v>12</v>
@@ -5415,14 +5491,14 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="47" t="n">
+      <c r="A198" s="48" t="n">
         <v>3</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C198" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D198" s="37" t="s">
         <v>15</v>
@@ -5438,7 +5514,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="47" t="n">
+      <c r="A199" s="48" t="n">
         <v>4</v>
       </c>
       <c r="B199" s="14" t="s">
@@ -5451,243 +5527,243 @@
         <v>18</v>
       </c>
       <c r="E199" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F199" s="37" t="s">
         <v>18</v>
       </c>
       <c r="G199" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="47" t="n">
+      <c r="A200" s="48" t="n">
         <v>5</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>19</v>
       </c>
       <c r="C200" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D200" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E200" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F200" s="37" t="s">
         <v>21</v>
       </c>
       <c r="G200" s="38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="47" t="n">
+      <c r="A201" s="48" t="n">
         <v>6</v>
       </c>
       <c r="B201" s="14" t="s">
         <v>21</v>
       </c>
       <c r="C201" s="37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D201" s="37" t="s">
         <v>22</v>
       </c>
       <c r="E201" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F201" s="37" t="s">
         <v>22</v>
       </c>
       <c r="G201" s="38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="47" t="n">
+      <c r="A202" s="48" t="n">
         <v>7</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C202" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="D202" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="D202" s="37" t="s">
-        <v>254</v>
-      </c>
       <c r="E202" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F202" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G202" s="38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="47" t="n">
+      <c r="A203" s="48" t="n">
         <v>8</v>
       </c>
       <c r="B203" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C203" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D203" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E203" s="37" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F203" s="37" t="s">
         <v>24</v>
       </c>
       <c r="G203" s="38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="47" t="n">
+      <c r="A204" s="48" t="n">
         <v>9</v>
       </c>
       <c r="B204" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C204" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="D204" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="D204" s="37" t="s">
+      <c r="E204" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="E204" s="37" t="s">
+      <c r="F204" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G204" s="38" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B205" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C205" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="F204" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="G204" s="38" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="B205" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="C205" s="37" t="s">
+      <c r="D205" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="D205" s="37" t="s">
+      <c r="E205" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="F205" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="G205" s="38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C206" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="D206" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="E205" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="F205" s="37" t="s">
+      <c r="E206" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F206" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="G205" s="38" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="206" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="47" t="n">
-        <v>11</v>
-      </c>
-      <c r="B206" s="14" t="s">
+      <c r="G206" s="38" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B207" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C206" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="D206" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="E206" s="37" t="s">
+      <c r="C207" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D207" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="F206" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="G206" s="38" t="s">
+      <c r="E207" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F207" s="37" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="207" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="47" t="n">
-        <v>12</v>
-      </c>
-      <c r="B207" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="C207" s="37" t="s">
+      <c r="G207" s="38" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B208" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C208" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D208" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="E208" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="F208" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="G208" s="38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C209" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D209" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E209" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="D207" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="E207" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="F207" s="37" t="s">
-        <v>263</v>
-      </c>
-      <c r="G207" s="38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="47" t="n">
-        <v>13</v>
-      </c>
-      <c r="B208" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C208" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="D208" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E208" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="F208" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="G208" s="38" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="47" t="n">
-        <v>14</v>
-      </c>
-      <c r="B209" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C209" s="37" t="s">
+      <c r="F209" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="G209" s="38" t="s">
         <v>270</v>
-      </c>
-      <c r="D209" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="E209" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="F209" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="G209" s="38" t="s">
-        <v>272</v>
       </c>
       <c r="I209" s="1"/>
       <c r="J209" s="2"/>
@@ -5698,7 +5774,7 @@
       <c r="O209" s="2"/>
     </row>
     <row r="210" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="47" t="n">
+      <c r="A210" s="48" t="n">
         <v>15</v>
       </c>
       <c r="B210" s="14" t="s">
@@ -5708,16 +5784,16 @@
         <v>12</v>
       </c>
       <c r="D210" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="E210" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="F210" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="G210" s="38" t="s">
         <v>273</v>
-      </c>
-      <c r="E210" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="F210" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G210" s="38" t="s">
-        <v>275</v>
       </c>
       <c r="I210" s="1"/>
       <c r="J210" s="2"/>
@@ -5728,23 +5804,23 @@
       <c r="O210" s="2"/>
     </row>
     <row r="211" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="47" t="n">
+      <c r="A211" s="48" t="n">
         <v>16</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>271</v>
       </c>
       <c r="C211" s="37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D211" s="37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E211" s="37" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F211" s="37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G211" s="38" t="s">
         <v>18</v>
@@ -5758,26 +5834,26 @@
       <c r="O211" s="2"/>
     </row>
     <row r="212" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="47" t="n">
+      <c r="A212" s="48" t="n">
         <v>17</v>
       </c>
       <c r="B212" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C212" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D212" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="C212" s="37" t="s">
+      <c r="E212" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="D212" s="37" t="s">
+      <c r="F212" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="G212" s="38" t="s">
         <v>280</v>
-      </c>
-      <c r="E212" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F212" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="G212" s="38" t="s">
-        <v>282</v>
       </c>
       <c r="I212" s="1"/>
       <c r="J212" s="2"/>
@@ -5788,26 +5864,26 @@
       <c r="O212" s="2"/>
     </row>
     <row r="213" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="47" t="n">
+      <c r="A213" s="48" t="n">
         <v>18</v>
       </c>
       <c r="B213" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C213" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D213" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="C213" s="37" t="s">
+      <c r="E213" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="D213" s="37" t="s">
+      <c r="F213" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="G213" s="38" t="s">
         <v>285</v>
-      </c>
-      <c r="E213" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="F213" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="G213" s="38" t="s">
-        <v>287</v>
       </c>
       <c r="I213" s="1"/>
       <c r="J213" s="2"/>
@@ -5818,1156 +5894,1188 @@
       <c r="O213" s="2"/>
     </row>
     <row r="214" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="47" t="n">
+      <c r="A214" s="48" t="n">
         <v>19</v>
       </c>
       <c r="B214" s="14" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C214" s="37" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D214" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="E214" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="F214" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="G214" s="38" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B215" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="E214" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="F214" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="G214" s="38" t="s">
+      <c r="C215" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D215" s="41" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="215" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="47" t="n">
-        <v>20</v>
-      </c>
-      <c r="B215" s="14" t="s">
+      <c r="E215" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="F215" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="G215" s="38" t="s">
         <v>290</v>
       </c>
-      <c r="C215" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="D215" s="37" t="s">
+    </row>
+    <row r="216" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="48" t="n">
+        <v>21</v>
+      </c>
+      <c r="B216" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C216" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="E215" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="F215" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="G215" s="38" t="s">
+      <c r="D216" s="37" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="216" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="47" t="n">
-        <v>21</v>
-      </c>
-      <c r="B216" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="C216" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="D216" s="37" t="s">
-        <v>295</v>
       </c>
       <c r="E216" s="37" t="s">
         <v>18</v>
       </c>
       <c r="F216" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="G216" s="38" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B217" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C217" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="D217" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="E217" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F217" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="G217" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="G216" s="38" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="217" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="47" t="n">
-        <v>22</v>
-      </c>
-      <c r="B217" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="C217" s="37" t="s">
+    </row>
+    <row r="218" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="48" t="n">
+        <v>23</v>
+      </c>
+      <c r="B218" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="D217" s="37" t="s">
+      <c r="C218" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="E217" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="F217" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="G217" s="38" t="s">
+      <c r="D218" s="41" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="218" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="47" t="n">
-        <v>23</v>
-      </c>
-      <c r="B218" s="14" t="s">
+      <c r="E218" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="C218" s="37" t="s">
+      <c r="F218" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="G218" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="D218" s="37" t="s">
+    </row>
+    <row r="219" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B219" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="E218" s="37" t="s">
+      <c r="C219" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="F218" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="G218" s="38" t="s">
+      <c r="D219" s="37" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="219" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="47" t="n">
-        <v>24</v>
-      </c>
-      <c r="B219" s="14" t="s">
+      <c r="E219" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="C219" s="37" t="s">
+      <c r="F219" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="G219" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="D219" s="37" t="s">
+    </row>
+    <row r="220" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="48" t="n">
+        <v>25</v>
+      </c>
+      <c r="B220" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C220" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="E219" s="37" t="s">
+      <c r="D220" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="F219" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="G219" s="38" t="s">
+      <c r="E220" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="F220" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="G220" s="38" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="47" t="n">
-        <v>25</v>
-      </c>
-      <c r="B220" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="C220" s="37" t="s">
+    <row r="221" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="B221" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="D220" s="37" t="s">
+      <c r="C221" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="E220" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="F220" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="G220" s="38" t="s">
+      <c r="D221" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E221" s="37" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="221" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="47" t="n">
-        <v>26</v>
-      </c>
-      <c r="B221" s="14" t="s">
+      <c r="F221" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G221" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="C221" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="D221" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="E221" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="F221" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="G221" s="38" t="s">
-        <v>316</v>
-      </c>
     </row>
     <row r="222" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="47" t="n">
+      <c r="A222" s="48" t="n">
         <v>27</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C222" s="37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D222" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="E222" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="F222" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="G222" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B223" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C223" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D223" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="E223" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="E222" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="F222" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="G222" s="38" t="s">
+      <c r="F223" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="G223" s="38" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="B223" s="14" t="s">
+    <row r="224" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="48" t="n">
+        <v>29</v>
+      </c>
+      <c r="B224" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="C223" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D223" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="E223" s="37" t="s">
+      <c r="C224" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="F223" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="G223" s="38" t="s">
+      <c r="D224" s="37" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="224" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="47" t="n">
-        <v>29</v>
-      </c>
-      <c r="B224" s="14" t="s">
+      <c r="E224" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="C224" s="37" t="s">
+      <c r="F224" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="G224" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="D224" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="E224" s="37" t="s">
+    </row>
+    <row r="225" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="B225" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="F224" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="G224" s="38" t="s">
+      <c r="C225" s="37" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="225" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="47" t="n">
-        <v>30</v>
-      </c>
-      <c r="B225" s="14" t="s">
+      <c r="D225" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="C225" s="37" t="s">
+      <c r="E225" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="D225" s="37" t="s">
+      <c r="F225" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="G225" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="E225" s="37" t="s">
+    </row>
+    <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="48" t="n">
+        <v>31</v>
+      </c>
+      <c r="B226" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="C226" s="37" t="s">
         <v>329</v>
       </c>
-      <c r="F225" s="37" t="s">
+      <c r="D226" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="E226" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F226" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="G226" s="38" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="48" t="n">
+        <v>32</v>
+      </c>
+      <c r="B227" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C227" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="D227" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="E227" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F227" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="G227" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="48" t="n">
+        <v>33</v>
+      </c>
+      <c r="B228" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C228" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="D228" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="E228" s="41" t="s">
         <v>328</v>
       </c>
-      <c r="G225" s="38" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="226" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="47" t="n">
-        <v>31</v>
-      </c>
-      <c r="B226" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C226" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="D226" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="E226" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="F226" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="G226" s="38" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="227" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="47" t="n">
-        <v>32</v>
-      </c>
-      <c r="B227" s="14" t="s">
-        <v>334</v>
-      </c>
-      <c r="C227" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="D227" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="E227" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F227" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="G227" s="38" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="228" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="47" t="n">
-        <v>33</v>
-      </c>
-      <c r="B228" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="C228" s="37" t="s">
+      <c r="F228" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="D228" s="37" t="s">
+      <c r="G228" s="38" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="48" t="n">
+        <v>34</v>
+      </c>
+      <c r="B229" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="E228" s="37" t="s">
+      <c r="C229" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="F228" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="G228" s="38" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="47" t="n">
-        <v>34</v>
-      </c>
-      <c r="B229" s="14" t="s">
+      <c r="D229" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="E229" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="C229" s="37" t="s">
+      <c r="F229" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="G229" s="38" t="s">
         <v>341</v>
       </c>
-      <c r="D229" s="37" t="s">
+    </row>
+    <row r="230" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="48" t="n">
+        <v>35</v>
+      </c>
+      <c r="B230" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C230" s="37" t="s">
         <v>342</v>
       </c>
-      <c r="E229" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="F229" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="G229" s="38" t="s">
+      <c r="D230" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="E230" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F230" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="G230" s="38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="48" t="n">
+        <v>36</v>
+      </c>
+      <c r="B231" s="14" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="230" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="47" t="n">
-        <v>35</v>
-      </c>
-      <c r="B230" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="C230" s="37" t="s">
+      <c r="C231" s="37" t="s">
         <v>344</v>
       </c>
-      <c r="D230" s="37" t="s">
+      <c r="D231" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="E230" s="37" t="s">
+      <c r="E231" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="F230" s="37" t="s">
+      <c r="F231" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="G230" s="38" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="231" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="B231" s="14" t="s">
+      <c r="G231" s="38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="48" t="n">
+        <v>37</v>
+      </c>
+      <c r="B232" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C232" s="37" t="s">
         <v>346</v>
       </c>
-      <c r="C231" s="37" t="s">
+      <c r="D232" s="37" t="s">
         <v>347</v>
       </c>
-      <c r="D231" s="37" t="s">
+      <c r="E232" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="F232" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="G232" s="38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="48" t="n">
+        <v>38</v>
+      </c>
+      <c r="B233" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C233" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="D233" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="E233" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="E231" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F231" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="G231" s="38" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="232" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="47" t="n">
-        <v>37</v>
-      </c>
-      <c r="B232" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="C232" s="37" t="s">
+      <c r="F233" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="G233" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="D232" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="E232" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="F232" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="G232" s="38" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="233" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="47" t="n">
-        <v>38</v>
-      </c>
-      <c r="B233" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C233" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="D233" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E233" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="F233" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G233" s="38" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="234" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="47" t="n">
+      <c r="A234" s="48" t="n">
         <v>39</v>
       </c>
       <c r="B234" s="14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C234" s="37" t="s">
         <v>44</v>
       </c>
       <c r="D234" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E234" s="37" t="s">
-        <v>353</v>
+        <v>350</v>
+      </c>
+      <c r="E234" s="41" t="s">
+        <v>351</v>
       </c>
       <c r="F234" s="37" t="s">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="G234" s="38" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="47" t="n">
+      <c r="A235" s="48" t="n">
         <v>40</v>
       </c>
       <c r="B235" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C235" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D235" s="37" t="s">
-        <v>86</v>
+      <c r="D235" s="41" t="s">
+        <v>352</v>
       </c>
       <c r="E235" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="F235" s="37" t="s">
-        <v>81</v>
+        <v>317</v>
+      </c>
+      <c r="F235" s="41" t="s">
+        <v>352</v>
       </c>
       <c r="G235" s="38" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="47" t="n">
+      <c r="A236" s="48" t="n">
         <v>41</v>
       </c>
       <c r="B236" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C236" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D236" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="E236" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="F236" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="G236" s="38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="48" t="n">
+        <v>42</v>
+      </c>
+      <c r="B237" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C237" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D237" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="E237" s="41" t="s">
         <v>355</v>
       </c>
-      <c r="E236" s="37" t="s">
-        <v>356</v>
-      </c>
-      <c r="F236" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="G236" s="38" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="237" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="B237" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C237" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D237" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="E237" s="37" t="s">
-        <v>358</v>
-      </c>
       <c r="F237" s="37" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G237" s="38" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="47" t="n">
+      <c r="A238" s="48" t="n">
         <v>43</v>
       </c>
       <c r="B238" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C238" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="D238" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="E238" s="37" t="s">
+        <v>358</v>
+      </c>
+      <c r="F238" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="G238" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B239" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="C238" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="D238" s="37" t="s">
+      <c r="C239" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="D239" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="E238" s="37" t="s">
+      <c r="E239" s="37" t="s">
         <v>361</v>
       </c>
-      <c r="F238" s="37" t="s">
+      <c r="F239" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="G238" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="B239" s="14" t="s">
+      <c r="G239" s="38" t="s">
         <v>362</v>
       </c>
-      <c r="C239" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="D239" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="E239" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="F239" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="G239" s="38" t="s">
-        <v>365</v>
-      </c>
     </row>
     <row r="240" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="47" t="n">
+      <c r="A240" s="48" t="n">
         <v>45</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C240" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D240" s="37" t="s">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="E240" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="F240" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G240" s="41" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C241" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D241" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E241" s="37" t="s">
         <v>366</v>
       </c>
-      <c r="F240" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="G240" s="38" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="241" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B241" s="14" t="s">
+      <c r="F241" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G241" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B242" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C242" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="C241" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="D241" s="37" t="s">
+      <c r="D242" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="E242" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="E241" s="37" t="s">
+      <c r="F242" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G242" s="38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B243" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="F241" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="G241" s="38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="242" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="47" t="n">
-        <v>47</v>
-      </c>
-      <c r="B242" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="C242" s="37" t="s">
+      <c r="C243" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="D242" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E242" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="F242" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G242" s="38" t="s">
+      <c r="D243" s="37" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="243" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="47" t="n">
-        <v>48</v>
-      </c>
-      <c r="B243" s="14" t="s">
+      <c r="E243" s="37" t="s">
         <v>372</v>
       </c>
-      <c r="C243" s="37" t="s">
+      <c r="F243" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="G243" s="38" t="s">
         <v>373</v>
       </c>
-      <c r="D243" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="E243" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="F243" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="G243" s="38" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="244" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="47" t="n">
+      <c r="A244" s="48" t="n">
         <v>49</v>
       </c>
       <c r="B244" s="14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C244" s="37" t="s">
         <v>62</v>
       </c>
       <c r="D244" s="37" t="s">
-        <v>28</v>
+        <v>374</v>
       </c>
       <c r="E244" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="F244" s="37" t="s">
+        <v>374</v>
+      </c>
+      <c r="G244" s="38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="48" t="n">
+        <v>50</v>
+      </c>
+      <c r="B245" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="F244" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="G244" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="245" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="47" t="n">
-        <v>50</v>
-      </c>
-      <c r="B245" s="14" t="s">
+      <c r="C245" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C245" s="37" t="s">
+      <c r="D245" s="37" t="s">
         <v>378</v>
       </c>
-      <c r="D245" s="37" t="s">
-        <v>345</v>
-      </c>
       <c r="E245" s="37" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="F245" s="37" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="G245" s="38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="48" t="n">
+        <v>51</v>
+      </c>
+      <c r="B246" s="14" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="246" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="B246" s="14" t="s">
+      <c r="C246" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D246" s="37" t="s">
         <v>380</v>
       </c>
-      <c r="C246" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="D246" s="37" t="s">
-        <v>328</v>
-      </c>
       <c r="E246" s="37" t="s">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="F246" s="37" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="G246" s="38" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="47" t="n">
+      <c r="A247" s="48" t="n">
         <v>52</v>
       </c>
       <c r="B247" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C247" s="37" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D247" s="37" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E247" s="37" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="F247" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="G247" s="38" t="s">
-        <v>383</v>
+        <v>281</v>
+      </c>
+      <c r="G247" s="41" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="47" t="n">
+      <c r="A248" s="48" t="n">
         <v>53</v>
       </c>
       <c r="B248" s="14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C248" s="37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D248" s="37" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E248" s="37" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="F248" s="37" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G248" s="38" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="47" t="n">
+      <c r="A249" s="48" t="n">
         <v>54</v>
       </c>
       <c r="B249" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C249" s="37" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D249" s="37" t="s">
-        <v>389</v>
+        <v>31</v>
       </c>
       <c r="E249" s="37" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="F249" s="37" t="s">
-        <v>389</v>
+        <v>31</v>
       </c>
       <c r="G249" s="38" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="47" t="n">
+      <c r="A250" s="48" t="n">
         <v>55</v>
       </c>
       <c r="B250" s="14" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C250" s="37" t="s">
         <v>32</v>
       </c>
       <c r="D250" s="37" t="s">
-        <v>32</v>
+        <v>391</v>
       </c>
       <c r="E250" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="F250" s="37" t="s">
         <v>391</v>
-      </c>
-      <c r="F250" s="37" t="s">
-        <v>32</v>
       </c>
       <c r="G250" s="38" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="47" t="n">
+      <c r="A251" s="48" t="n">
         <v>56</v>
       </c>
       <c r="B251" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C251" s="37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D251" s="37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E251" s="37" t="s">
-        <v>267</v>
+        <v>393</v>
       </c>
       <c r="F251" s="37" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G251" s="38" t="s">
-        <v>317</v>
+        <v>394</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="47" t="n">
+      <c r="A252" s="48" t="n">
         <v>57</v>
       </c>
       <c r="B252" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C252" s="37" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D252" s="37" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="E252" s="37" t="s">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="F252" s="37" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="G252" s="38" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="47" t="n">
+      <c r="A253" s="48" t="n">
         <v>58</v>
       </c>
       <c r="B253" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C253" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D253" s="37" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="E253" s="37" t="s">
-        <v>262</v>
+        <v>396</v>
       </c>
       <c r="F253" s="37" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
       <c r="G253" s="38" t="s">
-        <v>375</v>
+        <v>337</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="47" t="n">
+      <c r="A254" s="48" t="n">
         <v>59</v>
       </c>
       <c r="B254" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C254" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="D254" s="37"/>
+        <v>397</v>
+      </c>
+      <c r="D254" s="37" t="s">
+        <v>313</v>
+      </c>
       <c r="E254" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="F254" s="37"/>
+        <v>266</v>
+      </c>
+      <c r="F254" s="37" t="s">
+        <v>313</v>
+      </c>
       <c r="G254" s="38" t="s">
-        <v>317</v>
+        <v>398</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="47" t="n">
+      <c r="A255" s="48" t="n">
         <v>60</v>
       </c>
       <c r="B255" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C255" s="37" t="s">
-        <v>396</v>
-      </c>
-      <c r="D255" s="37"/>
+        <v>399</v>
+      </c>
+      <c r="D255" s="37" t="s">
+        <v>400</v>
+      </c>
       <c r="E255" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="F255" s="37"/>
+        <v>173</v>
+      </c>
+      <c r="F255" s="37" t="s">
+        <v>400</v>
+      </c>
       <c r="G255" s="38" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="47" t="n">
+      <c r="A256" s="48" t="n">
         <v>61</v>
       </c>
       <c r="B256" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C256" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D256" s="37"/>
+      <c r="D256" s="37" t="s">
+        <v>401</v>
+      </c>
       <c r="E256" s="37" t="s">
-        <v>396</v>
-      </c>
-      <c r="F256" s="37"/>
-      <c r="G256" s="38"/>
+        <v>261</v>
+      </c>
+      <c r="F256" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="G256" s="38" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="257" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="47" t="n">
+      <c r="A257" s="48" t="n">
         <v>62</v>
       </c>
       <c r="B257" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C257" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="D257" s="37"/>
+        <v>402</v>
+      </c>
+      <c r="D257" s="37" t="s">
+        <v>32</v>
+      </c>
       <c r="E257" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="F257" s="37"/>
-      <c r="G257" s="38"/>
+        <v>341</v>
+      </c>
+      <c r="F257" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G257" s="38" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="258" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="47" t="n">
+      <c r="A258" s="48" t="n">
         <v>63</v>
       </c>
       <c r="B258" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C258" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="D258" s="37"/>
+        <v>185</v>
+      </c>
+      <c r="D258" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="E258" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="F258" s="37"/>
+        <v>257</v>
+      </c>
+      <c r="F258" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="G258" s="38"/>
     </row>
     <row r="259" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="47" t="n">
+      <c r="A259" s="48" t="n">
         <v>64</v>
       </c>
       <c r="B259" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C259" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="D259" s="37"/>
+        <v>175</v>
+      </c>
+      <c r="D259" s="37" t="s">
+        <v>13</v>
+      </c>
       <c r="E259" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F259" s="37"/>
+        <v>399</v>
+      </c>
+      <c r="F259" s="37" t="s">
+        <v>13</v>
+      </c>
       <c r="G259" s="38"/>
     </row>
     <row r="260" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="47" t="n">
+      <c r="A260" s="48" t="n">
         <v>65</v>
       </c>
       <c r="B260" s="14" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C260" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D260" s="37"/>
+      <c r="D260" s="37" t="s">
+        <v>403</v>
+      </c>
       <c r="E260" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="F260" s="37"/>
+        <v>108</v>
+      </c>
+      <c r="F260" s="37" t="s">
+        <v>403</v>
+      </c>
       <c r="G260" s="38"/>
     </row>
     <row r="261" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="47" t="n">
+      <c r="A261" s="48" t="n">
         <v>66</v>
       </c>
       <c r="B261" s="14"/>
       <c r="C261" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="D261" s="37"/>
+        <v>310</v>
+      </c>
+      <c r="D261" s="0"/>
       <c r="E261" s="37" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="F261" s="37"/>
       <c r="G261" s="40"/>
     </row>
     <row r="262" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="47" t="n">
+      <c r="A262" s="48" t="n">
         <v>67</v>
       </c>
       <c r="B262" s="14"/>
       <c r="C262" s="37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E262" s="37" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="G262" s="40"/>
     </row>
     <row r="263" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="47" t="n">
+      <c r="A263" s="48" t="n">
         <v>68</v>
       </c>
       <c r="B263" s="14"/>
       <c r="C263" s="37" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E263" s="37" t="s">
-        <v>182</v>
+        <v>349</v>
       </c>
       <c r="G263" s="40"/>
     </row>
     <row r="264" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="47" t="n">
+      <c r="A264" s="48" t="n">
         <v>69</v>
       </c>
       <c r="B264" s="14"/>
       <c r="C264" s="37" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E264" s="37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G264" s="40"/>
     </row>
     <row r="265" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="47" t="n">
+      <c r="A265" s="48" t="n">
         <v>70</v>
       </c>
       <c r="B265" s="14"/>
       <c r="C265" s="37" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E265" s="37" t="s">
-        <v>402</v>
+        <v>32</v>
       </c>
       <c r="G265" s="40"/>
     </row>
     <row r="266" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="47" t="n">
+      <c r="A266" s="48" t="n">
         <v>71</v>
       </c>
       <c r="B266" s="14"/>
       <c r="C266" s="37" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E266" s="37" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="G266" s="40"/>
     </row>
     <row r="267" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="47" t="n">
+      <c r="A267" s="48" t="n">
         <v>72</v>
       </c>
       <c r="B267" s="14"/>
       <c r="C267" s="37" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E267" s="37" t="s">
-        <v>321</v>
+        <v>13</v>
       </c>
       <c r="G267" s="40"/>
     </row>
     <row r="268" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="47" t="n">
+      <c r="A268" s="48" t="n">
         <v>73</v>
       </c>
       <c r="B268" s="14"/>
       <c r="C268" s="37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E268" s="37" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="G268" s="40"/>
     </row>
     <row r="269" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="47" t="n">
+      <c r="A269" s="48" t="n">
         <v>74</v>
       </c>
       <c r="B269" s="14"/>
@@ -6975,49 +7083,56 @@
         <v>118</v>
       </c>
       <c r="E269" s="37" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
       <c r="G269" s="40"/>
     </row>
     <row r="270" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="47" t="n">
+      <c r="A270" s="48" t="n">
         <v>75</v>
       </c>
       <c r="B270" s="14"/>
       <c r="C270" s="37" t="s">
-        <v>404</v>
-      </c>
-      <c r="E270" s="37"/>
+        <v>410</v>
+      </c>
+      <c r="E270" s="37" t="s">
+        <v>318</v>
+      </c>
       <c r="G270" s="40"/>
     </row>
     <row r="271" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="47" t="n">
+      <c r="A271" s="48" t="n">
         <v>76</v>
       </c>
       <c r="B271" s="14"/>
       <c r="C271" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="E271" s="37"/>
+        <v>408</v>
+      </c>
+      <c r="E271" s="37" t="s">
+        <v>375</v>
+      </c>
       <c r="G271" s="40"/>
     </row>
     <row r="272" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="47" t="n">
+      <c r="A272" s="48" t="n">
         <v>77</v>
       </c>
       <c r="B272" s="14"/>
       <c r="C272" s="37" t="s">
         <v>17</v>
       </c>
+      <c r="E272" s="37" t="s">
+        <v>403</v>
+      </c>
       <c r="G272" s="40"/>
     </row>
     <row r="273" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="49" t="n">
+      <c r="A273" s="50" t="n">
         <v>78</v>
       </c>
-      <c r="B273" s="50"/>
-      <c r="C273" s="53" t="s">
-        <v>405</v>
+      <c r="B273" s="51"/>
+      <c r="C273" s="54" t="s">
+        <v>411</v>
       </c>
       <c r="D273" s="20"/>
       <c r="E273" s="20"/>
@@ -7035,16 +7150,16 @@
         <v>78</v>
       </c>
       <c r="D274" s="24" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E274" s="24" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F274" s="24" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G274" s="25" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H274" s="26"/>
       <c r="I274" s="26"/>
